--- a/Data/Qualitative analysis results/curated human.xlsx
+++ b/Data/Qualitative analysis results/curated human.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingqian/Desktop/msr_replication_package/Data/Qualitative analysis results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingqian/Desktop/PR_replication_package/Data/Qualitative analysis results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556CFDC7-4DD5-AF4E-8E24-B14B16E96AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FF37CA-EE19-C246-9787-8DE9D08EDC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3740" windowWidth="28040" windowHeight="17180" xr2:uid="{3A05C43E-DAAD-8848-9FF2-320DDEDB2F83}"/>
+    <workbookView xWindow="3240" yWindow="3680" windowWidth="28040" windowHeight="17180" xr2:uid="{3A05C43E-DAAD-8848-9FF2-320DDEDB2F83}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="217">
   <si>
     <t>curated human</t>
   </si>
@@ -512,12 +512,192 @@
   <si>
     <t>https://github.com/prebid/Prebid.js/pull/13610/commits/a9b576bdcb4b37eecb4b9a2b1330716ed4c7a8a0</t>
   </si>
+  <si>
+    <t>https://github.com/yairfalse/tapio/pull/149</t>
+  </si>
+  <si>
+    <t>https://github.com/beijaflor/tmuxrs/pull/14</t>
+  </si>
+  <si>
+    <t>https://github.com/credentum/agent-context-template/pull/99</t>
+  </si>
+  <si>
+    <t>https://github.com/credentum/agent-context-template/pull/104</t>
+  </si>
+  <si>
+    <t>https://github.com/carloseberhardt/threeaday/pull/3</t>
+  </si>
+  <si>
+    <t>https://github.com/rafaqat/swiftuionrails/pull/11</t>
+  </si>
+  <si>
+    <t>https://github.com/BibliothecaDAO/eternum/pull/3484</t>
+  </si>
+  <si>
+    <t>https://github.com/mk3008/rawsql-ts/pull/168</t>
+  </si>
+  <si>
+    <t>https://github.com/kamiazya/project-manager/pull/7</t>
+  </si>
+  <si>
+    <t>https://github.com/Automattic/mcp-server-gravatar-remote/pull/3</t>
+  </si>
+  <si>
+    <t>https://github.com/Kaniikura/certquiz/pull/53</t>
+  </si>
+  <si>
+    <t>https://github.com/chanzuckerberg/single-cell-data-portal/pull/7610</t>
+  </si>
+  <si>
+    <t>https://github.com/krhrtky/open-api-code-generator/pull/46</t>
+  </si>
+  <si>
+    <t>https://github.com/sog4be/sakurs/pull/24</t>
+  </si>
+  <si>
+    <t>https://github.com/rihib/www-rihib-dev/pull/59</t>
+  </si>
+  <si>
+    <t>https://github.com/hansjm10/adhdtodo/pull/51</t>
+  </si>
+  <si>
+    <t>https://github.com/TengHu/FactoryUI/pull/15</t>
+  </si>
+  <si>
+    <t>https://github.com/ophidiarium/cribo/pull/211</t>
+  </si>
+  <si>
+    <t>https://github.com/AppifySheets/Human-Readable-Calculation-Steps-Dotnet/pull/27</t>
+  </si>
+  <si>
+    <t>https://github.com/primeinc/file-analyzer/pull/10</t>
+  </si>
+  <si>
+    <t>https://github.com/BjornMelin/tripsage-ai/pull/127</t>
+  </si>
+  <si>
+    <t>https://github.com/safurrier/cookiecutter-ai-conventions/pull/26</t>
+  </si>
+  <si>
+    <t>https://github.com/pulakatlab/autoslide/pull/41</t>
+  </si>
+  <si>
+    <t>https://github.com/kazuya-tanimoto/freee-receipt-automation/pull/35</t>
+  </si>
+  <si>
+    <t>https://github.com/zeidalqadri/jsonderulo/pull/4</t>
+  </si>
+  <si>
+    <t>https://github.com/langadventurellc/trellis-mcp/pull/3</t>
+  </si>
+  <si>
+    <t>https://github.com/MemberJunction/MJ/pull/1068</t>
+  </si>
+  <si>
+    <t>https://github.com/Astroshaper/AsteroidShapeModels.jl/pull/52</t>
+  </si>
+  <si>
+    <t>https://github.com/yar0316/simple-architect-assistant/pull/10</t>
+  </si>
+  <si>
+    <t>https://github.com/RolandLittlehales/rustic-agent/pull/27</t>
+  </si>
+  <si>
+    <t>https://github.com/WilliamAGH/williamcallahan.com/pull/150</t>
+  </si>
+  <si>
+    <t>https://github.com/sophiedeziel/octoprint/pull/141</t>
+  </si>
+  <si>
+    <t>https://github.com/baleen37/dotfiles/pull/230</t>
+  </si>
+  <si>
+    <t>https://github.com/dasch-swiss/ark-resolver/pull/106</t>
+  </si>
+  <si>
+    <t>https://github.com/yifany-github/intelliSpark_ui/pull/43</t>
+  </si>
+  <si>
+    <t>https://github.com/nafg/dialogue-state/pull/87</t>
+  </si>
+  <si>
+    <t>https://github.com/huluobohua/storm-loop/pull/162</t>
+  </si>
+  <si>
+    <t>https://github.com/bluzky/prana/pull/23</t>
+  </si>
+  <si>
+    <t>https://github.com/obra/lace/pull/84</t>
+  </si>
+  <si>
+    <t>https://github.com/spencerduncan/balatro-rs/pull/657</t>
+  </si>
+  <si>
+    <t>https://github.com/claudes-world/cctoast-wsl/pull/48</t>
+  </si>
+  <si>
+    <t>https://github.com/jwilger/union_square/pull/153</t>
+  </si>
+  <si>
+    <t>https://github.com/MinBZK/poc-machine-law/pull/157</t>
+  </si>
+  <si>
+    <t>https://github.com/ophidiarium/cribo/pull/207</t>
+  </si>
+  <si>
+    <t>https://github.com/carbondirect/BOOST/pull/180</t>
+  </si>
+  <si>
+    <t>https://github.com/phrazzld/ponder/pull/5</t>
+  </si>
+  <si>
+    <t>https://github.com/BjornMelin/mcp-search-hub/pull/17</t>
+  </si>
+  <si>
+    <t>https://github.com/r-cz/iam-tools/pull/97</t>
+  </si>
+  <si>
+    <t>https://github.com/settlemint/asset-tokenization-kit/pull/2578</t>
+  </si>
+  <si>
+    <t>https://github.com/koki-develop/claude-code-team/pull/13</t>
+  </si>
+  <si>
+    <t>https://github.com/LLFourn/secp256kfun/pull/217</t>
+  </si>
+  <si>
+    <t>https://github.com/takeshishimada/Lockman/pull/131</t>
+  </si>
+  <si>
+    <t>https://github.com/nomadlabsinc/h2o/pull/41</t>
+  </si>
+  <si>
+    <t>direct removal</t>
+  </si>
+  <si>
+    <t>Direct removal</t>
+  </si>
+  <si>
+    <t>extract superclass</t>
+  </si>
+  <si>
+    <t>Parameterize method</t>
+  </si>
+  <si>
+    <t>extract class</t>
+  </si>
+  <si>
+    <t>pull up method</t>
+  </si>
+  <si>
+    <t>move method</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -548,6 +728,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -570,7 +757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -582,11 +769,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -922,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BA5BB9-A2E7-1447-9B39-3B69358DE6A5}">
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="12" max="12" width="26.6640625" customWidth="1"/>
@@ -935,20 +1123,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="5"/>
+      <c r="I1" s="7"/>
       <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
@@ -1042,10 +1230,10 @@
       <c r="K3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>69</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -1092,10 +1280,10 @@
       <c r="K4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>71</v>
       </c>
       <c r="N4" s="3" t="s">
@@ -1140,10 +1328,10 @@
       <c r="K5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>73</v>
       </c>
       <c r="N5" s="3" t="s">
@@ -1188,10 +1376,10 @@
       <c r="K6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>75</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -1238,10 +1426,10 @@
       <c r="K7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>77</v>
       </c>
       <c r="N7" s="3" t="s">
@@ -1286,10 +1474,10 @@
       <c r="K8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>79</v>
       </c>
       <c r="N8" s="3" t="s">
@@ -1334,10 +1522,10 @@
       <c r="K9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>81</v>
       </c>
       <c r="N9" s="3" t="s">
@@ -1380,10 +1568,10 @@
       <c r="K10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>83</v>
       </c>
       <c r="N10" s="3" t="s">
@@ -1428,10 +1616,10 @@
       <c r="K11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="6" t="s">
         <v>85</v>
       </c>
       <c r="N11" s="3" t="s">
@@ -1475,10 +1663,10 @@
       <c r="K12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6" t="s">
         <v>87</v>
       </c>
       <c r="N12" s="3" t="s">
@@ -1520,10 +1708,10 @@
       <c r="K13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="6" t="s">
         <v>89</v>
       </c>
       <c r="N13" s="3" t="s">
@@ -1565,10 +1753,10 @@
       <c r="K14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="M14" s="6" t="s">
         <v>91</v>
       </c>
       <c r="N14" s="3" t="s">
@@ -1610,10 +1798,10 @@
       <c r="K15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="L15" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="6" t="s">
         <v>93</v>
       </c>
       <c r="N15" s="3" t="s">
@@ -1655,10 +1843,10 @@
       <c r="K16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="6" t="s">
         <v>95</v>
       </c>
       <c r="N16" s="3" t="s">
@@ -1700,10 +1888,10 @@
       <c r="K17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="L17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="M17" s="6" t="s">
         <v>97</v>
       </c>
       <c r="N17" s="3" t="s">
@@ -1745,10 +1933,10 @@
       <c r="K18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="L18" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="M18" s="7" t="s">
+      <c r="M18" s="6" t="s">
         <v>99</v>
       </c>
       <c r="N18" s="3" t="s">
@@ -1790,10 +1978,10 @@
       <c r="K19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="L19" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="M19" s="7" t="s">
+      <c r="M19" s="6" t="s">
         <v>101</v>
       </c>
       <c r="N19" s="3" t="s">
@@ -1835,10 +2023,10 @@
       <c r="K20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="L20" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="M20" s="6" t="s">
         <v>103</v>
       </c>
       <c r="N20" s="3" t="s">
@@ -1880,10 +2068,10 @@
       <c r="K21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="L21" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="M21" s="6" t="s">
         <v>105</v>
       </c>
       <c r="N21" s="3" t="s">
@@ -1927,10 +2115,10 @@
       <c r="K22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="L22" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="M22" s="6" t="s">
         <v>107</v>
       </c>
       <c r="N22" s="3" t="s">
@@ -1974,10 +2162,10 @@
       <c r="K23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="L23" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="M23" s="6" t="s">
         <v>109</v>
       </c>
       <c r="N23" s="3" t="s">
@@ -2021,10 +2209,10 @@
       <c r="K24" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="L24" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="M24" s="7" t="s">
+      <c r="M24" s="6" t="s">
         <v>111</v>
       </c>
       <c r="N24" s="3" t="s">
@@ -2066,10 +2254,10 @@
       <c r="K25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="L25" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="M25" s="7" t="s">
+      <c r="M25" s="6" t="s">
         <v>113</v>
       </c>
       <c r="N25" s="3" t="s">
@@ -2113,10 +2301,10 @@
       <c r="K26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="L26" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="M26" s="7" t="s">
+      <c r="M26" s="6" t="s">
         <v>115</v>
       </c>
       <c r="N26" s="3" t="s">
@@ -2158,10 +2346,10 @@
       <c r="K27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="L27" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="M27" s="7" t="s">
+      <c r="M27" s="6" t="s">
         <v>117</v>
       </c>
       <c r="N27" s="3" t="s">
@@ -2205,10 +2393,10 @@
       <c r="K28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L28" s="7" t="s">
+      <c r="L28" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="M28" s="7" t="s">
+      <c r="M28" s="6" t="s">
         <v>119</v>
       </c>
       <c r="N28" s="3" t="s">
@@ -2250,10 +2438,10 @@
       <c r="K29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="L29" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="M29" s="6"/>
+      <c r="M29" s="5"/>
       <c r="N29" s="3" t="s">
         <v>44</v>
       </c>
@@ -2293,10 +2481,10 @@
       <c r="K30" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L30" s="7" t="s">
+      <c r="L30" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="M30" s="7" t="s">
+      <c r="M30" s="6" t="s">
         <v>122</v>
       </c>
       <c r="N30" s="3" t="s">
@@ -2338,10 +2526,10 @@
       <c r="K31" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="L31" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="M31" s="7" t="s">
+      <c r="M31" s="6" t="s">
         <v>124</v>
       </c>
       <c r="N31" s="3" t="s">
@@ -2383,10 +2571,10 @@
       <c r="K32" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="L32" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="M32" s="7" t="s">
+      <c r="M32" s="6" t="s">
         <v>126</v>
       </c>
       <c r="N32" s="3" t="s">
@@ -2428,10 +2616,10 @@
       <c r="K33" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L33" s="7" t="s">
+      <c r="L33" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="M33" s="7" t="s">
+      <c r="M33" s="6" t="s">
         <v>128</v>
       </c>
       <c r="N33" s="3" t="s">
@@ -2473,10 +2661,10 @@
       <c r="K34" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L34" s="7" t="s">
+      <c r="L34" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="M34" s="7" t="s">
+      <c r="M34" s="6" t="s">
         <v>130</v>
       </c>
       <c r="N34" s="3" t="s">
@@ -2518,10 +2706,10 @@
       <c r="K35" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="L35" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="M35" s="7" t="s">
+      <c r="M35" s="6" t="s">
         <v>132</v>
       </c>
       <c r="N35" s="3" t="s">
@@ -2565,10 +2753,10 @@
       <c r="K36" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L36" s="7" t="s">
+      <c r="L36" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="M36" s="7" t="s">
+      <c r="M36" s="6" t="s">
         <v>134</v>
       </c>
       <c r="N36" s="3" t="s">
@@ -2610,10 +2798,10 @@
       <c r="K37" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L37" s="7" t="s">
+      <c r="L37" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="M37" s="7" t="s">
+      <c r="M37" s="6" t="s">
         <v>136</v>
       </c>
       <c r="N37" s="3" t="s">
@@ -2657,10 +2845,10 @@
       <c r="K38" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="7" t="s">
+      <c r="L38" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="M38" s="7" t="s">
+      <c r="M38" s="6" t="s">
         <v>138</v>
       </c>
       <c r="N38" s="3" t="s">
@@ -2702,10 +2890,10 @@
       <c r="K39" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="7" t="s">
+      <c r="L39" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M39" s="7" t="s">
+      <c r="M39" s="6" t="s">
         <v>140</v>
       </c>
       <c r="N39" s="3" t="s">
@@ -2747,10 +2935,10 @@
       <c r="K40" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L40" s="7" t="s">
+      <c r="L40" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="M40" s="7" t="s">
+      <c r="M40" s="6" t="s">
         <v>142</v>
       </c>
       <c r="N40" s="3" t="s">
@@ -2792,10 +2980,10 @@
       <c r="K41" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L41" s="7" t="s">
+      <c r="L41" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M41" s="7" t="s">
+      <c r="M41" s="6" t="s">
         <v>144</v>
       </c>
       <c r="N41" s="3" t="s">
@@ -2837,10 +3025,10 @@
       <c r="K42" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L42" s="7" t="s">
+      <c r="L42" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="M42" s="7" t="s">
+      <c r="M42" s="6" t="s">
         <v>146</v>
       </c>
       <c r="N42" s="3" t="s">
@@ -2884,10 +3072,10 @@
       <c r="K43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L43" s="7" t="s">
+      <c r="L43" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="M43" s="7" t="s">
+      <c r="M43" s="6" t="s">
         <v>148</v>
       </c>
       <c r="N43" s="3" t="s">
@@ -2931,10 +3119,10 @@
       <c r="K44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L44" s="7" t="s">
+      <c r="L44" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="M44" s="7" t="s">
+      <c r="M44" s="6" t="s">
         <v>150</v>
       </c>
       <c r="N44" s="3" t="s">
@@ -2976,10 +3164,10 @@
       <c r="K45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L45" s="7" t="s">
+      <c r="L45" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="M45" s="7" t="s">
+      <c r="M45" s="6" t="s">
         <v>152</v>
       </c>
       <c r="N45" s="3" t="s">
@@ -3026,10 +3214,10 @@
       <c r="K46" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L46" s="7" t="s">
+      <c r="L46" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="M46" s="7" t="s">
+      <c r="M46" s="6" t="s">
         <v>154</v>
       </c>
       <c r="N46" s="3" t="s">
@@ -3071,10 +3259,10 @@
       <c r="K47" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L47" s="7" t="s">
+      <c r="L47" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="M47" s="7" t="s">
+      <c r="M47" s="6" t="s">
         <v>156</v>
       </c>
       <c r="N47" s="3" t="s">
@@ -3085,16 +3273,2263 @@
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" s="8">
+        <v>3264710298</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="O48" s="4"/>
     </row>
-    <row r="49" spans="15:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A49" s="8">
+        <v>3265400619</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="O49" s="4"/>
     </row>
-    <row r="50" spans="15:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
+        <v>3234033710</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="O50" s="4"/>
     </row>
-    <row r="51" spans="15:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A51" s="8">
+        <v>3234076563</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
+        <v>3213894476</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A53" s="8">
+        <v>3215410323</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A54" s="8">
+        <v>3217092959</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A55" s="8">
+        <v>3218898737</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" s="8">
+        <v>3220180204</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A57" s="8">
+        <v>3221195362</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58" s="8">
+        <v>3246385831</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59" s="8">
+        <v>3141697967</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60" s="8">
+        <v>3165754522</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A61" s="8">
+        <v>3200463798</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
+        <v>3250965406</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A63" s="8">
+        <v>3106313663</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A64" s="8">
+        <v>3245740917</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A65" s="8">
+        <v>3260516091</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A66" s="8">
+        <v>3187709515</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A67" s="8">
+        <v>3085182717</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
+        <v>3087697940</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
+        <v>3135236993</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A70" s="8">
+        <v>3205465689</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A71" s="8">
+        <v>3248781517</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A72" s="8">
+        <v>3175376782</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A73" s="8">
+        <v>3266892277</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A74" s="8">
+        <v>3229546455</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A75" s="8">
+        <v>3161681645</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A76" s="8">
+        <v>3253280337</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A77" s="8">
+        <v>3195145062</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A78" s="8">
+        <v>3167406746</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A79" s="8">
+        <v>3208990831</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A80" s="8">
+        <v>3185578768</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A81" s="8">
+        <v>3185645561</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A82" s="8">
+        <v>3185708722</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A83" s="8">
+        <v>3236357981</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A84" s="8">
+        <v>3271296688</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="N84" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A85" s="8">
+        <v>3238176826</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A86" s="8">
+        <v>3240890263</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A87" s="8">
+        <v>3241745415</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A88" s="8">
+        <v>3241945321</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="N88" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A89" s="8">
+        <v>3267485271</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A90" s="8">
+        <v>3267732170</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="N90" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A91" s="8">
+        <v>3267957812</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A92" s="8">
+        <v>3256302405</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="N92" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A93" s="8">
+        <v>3257766913</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="N93" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A94" s="8">
+        <v>3257887882</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A95" s="8">
+        <v>3069010262</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="N95" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A96" s="8">
+        <v>3070213329</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A97" s="8">
+        <v>3071047437</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A98" s="8">
+        <v>3172162764</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A99" s="8">
+        <v>3158527730</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A100" s="8">
+        <v>3158818689</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A101" s="8">
+        <v>3206377463</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L101" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A102" s="8">
+        <v>3131933230</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L102" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>216</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3192,6 +5627,61 @@
     <hyperlink ref="M46" r:id="rId87" xr:uid="{CEC2851F-C031-3A49-9F94-37034F8D64CA}"/>
     <hyperlink ref="L47" r:id="rId88" xr:uid="{9FBB0510-FD8B-A64B-99C2-327B55FD4F40}"/>
     <hyperlink ref="M47" r:id="rId89" xr:uid="{C4C8CF2E-01F7-424F-8263-B7CA54CF13AC}"/>
+    <hyperlink ref="L48" r:id="rId90" xr:uid="{8928AE06-C593-B440-AC61-22E6641CD3C8}"/>
+    <hyperlink ref="L49" r:id="rId91" xr:uid="{958AB1CD-2AB6-C741-A896-5A7E298E604A}"/>
+    <hyperlink ref="L50" r:id="rId92" xr:uid="{190B8AA0-98BC-114E-BC47-06A333D8777B}"/>
+    <hyperlink ref="L51" r:id="rId93" xr:uid="{3AAB44AB-4814-F147-9192-C54349B7D373}"/>
+    <hyperlink ref="L52" r:id="rId94" xr:uid="{A09610D6-FF78-4344-8CA2-66DB8267A169}"/>
+    <hyperlink ref="L53" r:id="rId95" xr:uid="{D4ECD304-54BB-934D-91B6-A78381F2349F}"/>
+    <hyperlink ref="L54" r:id="rId96" xr:uid="{A40B1AC9-E4C2-D94D-AA45-EAE7EC67806A}"/>
+    <hyperlink ref="L55" r:id="rId97" xr:uid="{675A934B-3A30-0940-9807-FEB086C9C993}"/>
+    <hyperlink ref="L56" r:id="rId98" xr:uid="{A5434389-D348-674E-949C-ECBAF53E7B58}"/>
+    <hyperlink ref="L57" r:id="rId99" xr:uid="{38CB563F-92C7-2143-9594-7C337970E240}"/>
+    <hyperlink ref="L58" r:id="rId100" xr:uid="{04227A95-7F27-B846-B106-F3DE3BB7765F}"/>
+    <hyperlink ref="L59" r:id="rId101" xr:uid="{10E70937-5BC4-E341-9DE3-91ACD8D824B5}"/>
+    <hyperlink ref="L60" r:id="rId102" xr:uid="{4AC233A8-5068-664E-9815-3DED0D82ED2E}"/>
+    <hyperlink ref="L61" r:id="rId103" xr:uid="{E69F39C3-DDF9-8842-ACFC-720459DCE021}"/>
+    <hyperlink ref="L62" r:id="rId104" xr:uid="{F513A4C0-5110-4C42-9E1F-DC3EE060C6E3}"/>
+    <hyperlink ref="L63" r:id="rId105" xr:uid="{36DD74C6-5E24-F242-A97D-11FA00F7C581}"/>
+    <hyperlink ref="L64" r:id="rId106" xr:uid="{12AE26D5-385C-F74B-A4D0-5FF5FDB91ED8}"/>
+    <hyperlink ref="L65" r:id="rId107" xr:uid="{6BA6FF94-5D03-794B-90A1-45938A94E545}"/>
+    <hyperlink ref="L66" r:id="rId108" xr:uid="{16E709CB-28C3-CD43-B1C7-C484580B7B51}"/>
+    <hyperlink ref="L67" r:id="rId109" xr:uid="{95326192-61F9-DA4A-8E36-168C69A1D038}"/>
+    <hyperlink ref="L68" r:id="rId110" xr:uid="{9A9D8365-FCE2-994A-8B92-AC767172F275}"/>
+    <hyperlink ref="L69" r:id="rId111" xr:uid="{B561989A-AB10-AD4D-B6B3-50DB4D256345}"/>
+    <hyperlink ref="L70" r:id="rId112" xr:uid="{5ADEB452-787E-CE46-AEE2-3DCAD23227A4}"/>
+    <hyperlink ref="L71" r:id="rId113" xr:uid="{88C03F14-A05E-B343-BC30-0E2CF8958FEF}"/>
+    <hyperlink ref="L72" r:id="rId114" xr:uid="{C07F4566-CDE0-1244-8842-7312EE73E5A8}"/>
+    <hyperlink ref="L73" r:id="rId115" xr:uid="{5AD54F11-D283-BF4F-B83C-9900709B4E0F}"/>
+    <hyperlink ref="L74" r:id="rId116" xr:uid="{A0956D04-DE3E-C94F-A93E-AF3AE53DAB80}"/>
+    <hyperlink ref="L75" r:id="rId117" xr:uid="{B2597A99-32AE-7F45-A738-CCACDB7F569C}"/>
+    <hyperlink ref="L76" r:id="rId118" xr:uid="{B3305D4E-9C22-5749-859C-1156D4224E3B}"/>
+    <hyperlink ref="L77" r:id="rId119" xr:uid="{E59EEF14-8B76-D048-8F60-DA9BF7090D44}"/>
+    <hyperlink ref="L78" r:id="rId120" xr:uid="{3A665FB9-6188-3F4A-BB2D-F68B33F5669C}"/>
+    <hyperlink ref="L79" r:id="rId121" xr:uid="{3C96CBD3-FBE5-544F-97F1-EB519A83FD7D}"/>
+    <hyperlink ref="L80" r:id="rId122" xr:uid="{58718B83-6594-634D-9E9E-17613AFECC4F}"/>
+    <hyperlink ref="L81" r:id="rId123" xr:uid="{04F1F7CD-2353-3046-8CA5-8CE0808E46CA}"/>
+    <hyperlink ref="L82" r:id="rId124" xr:uid="{668E55B4-9041-DC40-B74D-4F1AFCAF9B99}"/>
+    <hyperlink ref="L83" r:id="rId125" xr:uid="{211C46F0-0FE5-3F42-A401-3CD9173DDBB4}"/>
+    <hyperlink ref="L84" r:id="rId126" xr:uid="{215D298D-32CC-B44D-AEB3-B8D4DB482FCE}"/>
+    <hyperlink ref="L85" r:id="rId127" xr:uid="{7D315671-A8DC-DF42-B0F1-C6DA92D10806}"/>
+    <hyperlink ref="L86" r:id="rId128" xr:uid="{1253EDF5-F588-E645-8298-6C27F0EF6C46}"/>
+    <hyperlink ref="L87" r:id="rId129" xr:uid="{51D217B9-C4CB-6644-A7EA-EB12B97CFB98}"/>
+    <hyperlink ref="L88" r:id="rId130" xr:uid="{946AB6ED-6B01-8E4E-89AE-A9F779B23758}"/>
+    <hyperlink ref="L89" r:id="rId131" xr:uid="{E9B0E542-CFA8-F04F-8472-C8FFC02FD9D8}"/>
+    <hyperlink ref="L90" r:id="rId132" xr:uid="{59BEA31D-DA69-6341-AC88-84EA1F4520D3}"/>
+    <hyperlink ref="L91" r:id="rId133" xr:uid="{82C96613-A68C-9241-8E70-EA412CAD8710}"/>
+    <hyperlink ref="L92" r:id="rId134" xr:uid="{23DE5D3C-F571-F145-B633-F51C4AE69471}"/>
+    <hyperlink ref="L93" r:id="rId135" xr:uid="{D70DFBA0-CEB9-4E4E-8339-5376ED37BC09}"/>
+    <hyperlink ref="L94" r:id="rId136" xr:uid="{B5D1D06D-4E35-A343-8D31-45DA2397ED75}"/>
+    <hyperlink ref="L95" r:id="rId137" xr:uid="{0022E938-E066-494A-988D-B6C4D348647F}"/>
+    <hyperlink ref="L96" r:id="rId138" xr:uid="{8CA448FE-E102-EF4F-B07D-C2CDED7EFD78}"/>
+    <hyperlink ref="L97" r:id="rId139" xr:uid="{81636735-64D2-FC42-BEDF-1A620AD0ECAB}"/>
+    <hyperlink ref="L98" r:id="rId140" xr:uid="{09E07886-F160-5448-8FF0-428E66E900C3}"/>
+    <hyperlink ref="L99" r:id="rId141" xr:uid="{0BC1A091-98C3-1647-B623-4B56AFFD72C1}"/>
+    <hyperlink ref="L100" r:id="rId142" xr:uid="{5960B614-8752-F54D-B556-514EC4D019EA}"/>
+    <hyperlink ref="L101" r:id="rId143" xr:uid="{CD384461-A76E-6A42-A53F-1BFA05E2D9D0}"/>
+    <hyperlink ref="L102" r:id="rId144" xr:uid="{0F3044CB-DE98-F841-A1E2-40A11E7B120C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
